--- a/templates/Rechnung_Vorlage_v4.xlsx
+++ b/templates/Rechnung_Vorlage_v4.xlsx
@@ -700,13 +700,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>448235</xdr:colOff>
+      <xdr:colOff>688235</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>107198</xdr:colOff>
+      <xdr:colOff>347198</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>44825</xdr:rowOff>
     </xdr:to>
@@ -737,7 +737,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4728882" y="0"/>
+          <a:off x="4968882" y="0"/>
           <a:ext cx="2269934" cy="1815354"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/templates/Rechnung_Vorlage_v4.xlsx
+++ b/templates/Rechnung_Vorlage_v4.xlsx
@@ -700,13 +700,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>688235</xdr:colOff>
+      <xdr:colOff>614535</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>347198</xdr:colOff>
+      <xdr:colOff>43498</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>44825</xdr:rowOff>
     </xdr:to>
@@ -737,8 +737,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4968882" y="0"/>
-          <a:ext cx="2269934" cy="1815354"/>
+          <a:off x="4895182" y="0"/>
+          <a:ext cx="2039934" cy="1631414"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
